--- a/Vectra Staffing LLC Employee Directory.xlsx
+++ b/Vectra Staffing LLC Employee Directory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\ERP-System-Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181E6F41-EE8A-432A-AC0A-F6DFD9577BAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91447CF9-4225-4477-9C0D-FF7906C3D1B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19422" windowHeight="10302" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="136">
   <si>
     <t>Employee joining, designation, and contact records | Updated for 2025–2026</t>
   </si>
@@ -422,6 +422,12 @@
   </si>
   <si>
     <t>Done</t>
+  </si>
+  <si>
+    <t>Column 4</t>
+  </si>
+  <si>
+    <t>Updated Week 3</t>
   </si>
 </sst>
 </file>
@@ -694,6 +700,9 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -701,9 +710,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -711,7 +717,33 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -879,17 +911,6 @@
         <scheme val="major"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -904,17 +925,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:I38" dataDxfId="9">
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:J38" dataDxfId="11">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{95819C09-FC15-4B97-8E78-01BF41FCFA5C}" name="Column 4" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1069,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10.76171875" bestFit="1" customWidth="1"/>
@@ -1080,39 +1102,40 @@
     <col min="7" max="7" width="39.046875" customWidth="1"/>
     <col min="8" max="8" width="32.09375" customWidth="1"/>
     <col min="9" max="9" width="27.37890625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21.4" customHeight="1">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:10" ht="21.4" customHeight="1">
+      <c r="A1" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.65" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+    </row>
+    <row r="2" spans="1:10" ht="14.65" customHeight="1">
+      <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-    </row>
-    <row r="3" spans="1:9" ht="13.45" customHeight="1">
-      <c r="A3" s="31" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+    </row>
+    <row r="3" spans="1:10" ht="13.45" customHeight="1">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-    </row>
-    <row r="5" spans="1:9" ht="16.649999999999999" customHeight="1">
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+    </row>
+    <row r="5" spans="1:10" ht="16.649999999999999" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1140,8 +1163,11 @@
       <c r="I5" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.4">
+      <c r="J5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="14.4">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
@@ -1150,11 +1176,12 @@
       <c r="F6" s="19"/>
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
-      <c r="I6" s="32" t="s">
+      <c r="I6" s="29" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.4">
+      <c r="J6" s="24"/>
+    </row>
+    <row r="7" spans="1:10" ht="14.4">
       <c r="A7" s="6">
         <v>2</v>
       </c>
@@ -1182,8 +1209,11 @@
       <c r="I7" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="14.4">
+      <c r="J7" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="14.4">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -1211,8 +1241,11 @@
       <c r="I8" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="14.4">
+      <c r="J8" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="14.4">
       <c r="A9" s="6">
         <v>4</v>
       </c>
@@ -1238,8 +1271,11 @@
       <c r="I9" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="14.4">
+      <c r="J9" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="14.4">
       <c r="A10" s="10">
         <v>5</v>
       </c>
@@ -1267,8 +1303,11 @@
       <c r="I10" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.4">
+      <c r="J10" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="14.4">
       <c r="A11" s="6">
         <v>6</v>
       </c>
@@ -1294,8 +1333,11 @@
       <c r="I11" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.4">
+      <c r="J11" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="14.4">
       <c r="A12" s="10">
         <v>7</v>
       </c>
@@ -1323,8 +1365,11 @@
       <c r="I12" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.4">
+      <c r="J12" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="14.4">
       <c r="A13" s="6">
         <v>8</v>
       </c>
@@ -1352,8 +1397,9 @@
       <c r="I13" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.4">
+      <c r="J13" s="24"/>
+    </row>
+    <row r="14" spans="1:10" ht="14.4">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
@@ -1363,8 +1409,9 @@
       <c r="G14" s="24"/>
       <c r="H14" s="24"/>
       <c r="I14" s="24"/>
-    </row>
-    <row r="15" spans="1:9" ht="14.4">
+      <c r="J14" s="24"/>
+    </row>
+    <row r="15" spans="1:10" ht="14.4">
       <c r="A15" s="6">
         <v>10</v>
       </c>
@@ -1386,8 +1433,9 @@
       <c r="G15" s="24"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
-    </row>
-    <row r="16" spans="1:9" ht="14.4">
+      <c r="J15" s="24"/>
+    </row>
+    <row r="16" spans="1:10" ht="14.4">
       <c r="A16" s="10">
         <v>11</v>
       </c>
@@ -1415,8 +1463,9 @@
       <c r="I16" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.4">
+      <c r="J16" s="24"/>
+    </row>
+    <row r="17" spans="1:10" ht="14.4">
       <c r="A17" s="6">
         <v>12</v>
       </c>
@@ -1444,8 +1493,9 @@
       <c r="I17" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="14.4">
+      <c r="J17" s="24"/>
+    </row>
+    <row r="18" spans="1:10" ht="14.4">
       <c r="A18" s="10">
         <v>13</v>
       </c>
@@ -1471,8 +1521,9 @@
         <v>122</v>
       </c>
       <c r="I18" s="24"/>
-    </row>
-    <row r="19" spans="1:9" ht="14.4">
+      <c r="J18" s="24"/>
+    </row>
+    <row r="19" spans="1:10" ht="14.4">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
@@ -1482,8 +1533,9 @@
       <c r="G19" s="24"/>
       <c r="H19" s="24"/>
       <c r="I19" s="24"/>
-    </row>
-    <row r="20" spans="1:9" ht="14.4">
+      <c r="J19" s="24"/>
+    </row>
+    <row r="20" spans="1:10" ht="14.4">
       <c r="A20" s="10">
         <v>15</v>
       </c>
@@ -1507,8 +1559,9 @@
       </c>
       <c r="H20" s="24"/>
       <c r="I20" s="24"/>
-    </row>
-    <row r="21" spans="1:9" ht="14.4">
+      <c r="J20" s="24"/>
+    </row>
+    <row r="21" spans="1:10" ht="14.4">
       <c r="A21" s="6">
         <v>16</v>
       </c>
@@ -1536,8 +1589,9 @@
       <c r="I21" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="14.4">
+      <c r="J21" s="24"/>
+    </row>
+    <row r="22" spans="1:10" ht="14.4">
       <c r="A22" s="10">
         <v>17</v>
       </c>
@@ -1565,8 +1619,9 @@
       <c r="I22" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="14.4">
+      <c r="J22" s="24"/>
+    </row>
+    <row r="23" spans="1:10" ht="14.4">
       <c r="A23" s="6">
         <v>18</v>
       </c>
@@ -1594,8 +1649,9 @@
       <c r="I23" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="14.4">
+      <c r="J23" s="24"/>
+    </row>
+    <row r="24" spans="1:10" ht="14.4">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12"/>
@@ -1605,8 +1661,9 @@
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
-    </row>
-    <row r="25" spans="1:9" ht="14.4">
+      <c r="J24" s="24"/>
+    </row>
+    <row r="25" spans="1:10" ht="14.4">
       <c r="A25" s="6">
         <v>20</v>
       </c>
@@ -1634,8 +1691,9 @@
       <c r="I25" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="14.4">
+      <c r="J25" s="24"/>
+    </row>
+    <row r="26" spans="1:10" ht="14.4">
       <c r="A26" s="10">
         <v>21</v>
       </c>
@@ -1663,8 +1721,9 @@
       <c r="I26" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="14.4">
+      <c r="J26" s="24"/>
+    </row>
+    <row r="27" spans="1:10" ht="14.4">
       <c r="A27" s="6">
         <v>22</v>
       </c>
@@ -1692,8 +1751,9 @@
       <c r="I27" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="14.4">
+      <c r="J27" s="24"/>
+    </row>
+    <row r="28" spans="1:10" ht="14.4">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12"/>
@@ -1703,8 +1763,9 @@
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
       <c r="I28" s="24"/>
-    </row>
-    <row r="29" spans="1:9" ht="14.4">
+      <c r="J28" s="24"/>
+    </row>
+    <row r="29" spans="1:10" ht="14.4">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
@@ -1714,8 +1775,9 @@
       <c r="G29" s="24"/>
       <c r="H29" s="24"/>
       <c r="I29" s="24"/>
-    </row>
-    <row r="30" spans="1:9" ht="14.4">
+      <c r="J29" s="24"/>
+    </row>
+    <row r="30" spans="1:10" ht="14.4">
       <c r="A30" s="10">
         <v>25</v>
       </c>
@@ -1743,8 +1805,9 @@
       <c r="I30" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="14.4">
+      <c r="J30" s="24"/>
+    </row>
+    <row r="31" spans="1:10" ht="14.4">
       <c r="A31" s="6">
         <v>26</v>
       </c>
@@ -1772,8 +1835,9 @@
       <c r="I31" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="14.4">
+      <c r="J31" s="24"/>
+    </row>
+    <row r="32" spans="1:10" ht="14.4">
       <c r="A32" s="10">
         <v>27</v>
       </c>
@@ -1801,8 +1865,9 @@
       <c r="I32" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="14.4">
+      <c r="J32" s="24"/>
+    </row>
+    <row r="33" spans="1:10" ht="14.4">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="8"/>
@@ -1812,8 +1877,9 @@
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
       <c r="I33" s="24"/>
-    </row>
-    <row r="34" spans="1:9" ht="14.4">
+      <c r="J33" s="24"/>
+    </row>
+    <row r="34" spans="1:10" ht="14.4">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -1841,8 +1907,9 @@
       <c r="I34" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="14.4">
+      <c r="J34" s="24"/>
+    </row>
+    <row r="35" spans="1:10" ht="14.4">
       <c r="A35" s="6">
         <v>30</v>
       </c>
@@ -1870,8 +1937,9 @@
       <c r="I35" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="14.4">
+      <c r="J35" s="24"/>
+    </row>
+    <row r="36" spans="1:10" ht="14.4">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -1893,8 +1961,9 @@
       <c r="G36" s="24"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
-    </row>
-    <row r="37" spans="1:9" ht="14.4">
+      <c r="J36" s="24"/>
+    </row>
+    <row r="37" spans="1:10" ht="14.4">
       <c r="A37" s="6">
         <v>32</v>
       </c>
@@ -1922,8 +1991,9 @@
       <c r="I37" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="14.4">
+      <c r="J37" s="24"/>
+    </row>
+    <row r="38" spans="1:10" ht="14.4">
       <c r="A38" s="15">
         <v>33</v>
       </c>
@@ -1949,6 +2019,7 @@
         <v>123</v>
       </c>
       <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1957,7 +2028,7 @@
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D20 D23 D25:D38">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>D6="Not Available"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Vectra Staffing LLC Employee Directory.xlsx
+++ b/Vectra Staffing LLC Employee Directory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\ERP-System-Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91447CF9-4225-4477-9C0D-FF7906C3D1B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181E6F41-EE8A-432A-AC0A-F6DFD9577BAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19422" windowHeight="10302" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="134">
   <si>
     <t>Employee joining, designation, and contact records | Updated for 2025–2026</t>
   </si>
@@ -422,12 +422,6 @@
   </si>
   <si>
     <t>Done</t>
-  </si>
-  <si>
-    <t>Column 4</t>
-  </si>
-  <si>
-    <t>Updated Week 3</t>
   </si>
 </sst>
 </file>
@@ -700,9 +694,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -710,6 +701,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -717,33 +711,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <strike val="0"/>
@@ -911,6 +879,17 @@
         <scheme val="major"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -925,18 +904,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:J38" dataDxfId="11">
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{95819C09-FC15-4B97-8E78-01BF41FCFA5C}" name="Column 4" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:I38" dataDxfId="9">
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1091,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10.76171875" bestFit="1" customWidth="1"/>
@@ -1102,40 +1080,39 @@
     <col min="7" max="7" width="39.046875" customWidth="1"/>
     <col min="8" max="8" width="32.09375" customWidth="1"/>
     <col min="9" max="9" width="27.37890625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.4" customHeight="1">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:9" ht="21.4" customHeight="1">
+      <c r="A1" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.65" customHeight="1">
-      <c r="A2" s="31" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+    </row>
+    <row r="2" spans="1:9" ht="14.65" customHeight="1">
+      <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-    </row>
-    <row r="3" spans="1:10" ht="13.45" customHeight="1">
-      <c r="A3" s="32" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="3" spans="1:9" ht="13.45" customHeight="1">
+      <c r="A3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-    </row>
-    <row r="5" spans="1:10" ht="16.649999999999999" customHeight="1">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+    </row>
+    <row r="5" spans="1:9" ht="16.649999999999999" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1163,11 +1140,8 @@
       <c r="I5" t="s">
         <v>131</v>
       </c>
-      <c r="J5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="14.4">
+    </row>
+    <row r="6" spans="1:9" ht="14.4">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
@@ -1176,12 +1150,11 @@
       <c r="F6" s="19"/>
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="J6" s="24"/>
-    </row>
-    <row r="7" spans="1:10" ht="14.4">
+    </row>
+    <row r="7" spans="1:9" ht="14.4">
       <c r="A7" s="6">
         <v>2</v>
       </c>
@@ -1209,11 +1182,8 @@
       <c r="I7" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J7" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="14.4">
+    </row>
+    <row r="8" spans="1:9" ht="14.4">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -1241,11 +1211,8 @@
       <c r="I8" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J8" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="14.4">
+    </row>
+    <row r="9" spans="1:9" ht="14.4">
       <c r="A9" s="6">
         <v>4</v>
       </c>
@@ -1271,11 +1238,8 @@
       <c r="I9" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J9" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="14.4">
+    </row>
+    <row r="10" spans="1:9" ht="14.4">
       <c r="A10" s="10">
         <v>5</v>
       </c>
@@ -1303,11 +1267,8 @@
       <c r="I10" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J10" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="14.4">
+    </row>
+    <row r="11" spans="1:9" ht="14.4">
       <c r="A11" s="6">
         <v>6</v>
       </c>
@@ -1333,11 +1294,8 @@
       <c r="I11" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J11" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="14.4">
+    </row>
+    <row r="12" spans="1:9" ht="14.4">
       <c r="A12" s="10">
         <v>7</v>
       </c>
@@ -1365,11 +1323,8 @@
       <c r="I12" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J12" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="14.4">
+    </row>
+    <row r="13" spans="1:9" ht="14.4">
       <c r="A13" s="6">
         <v>8</v>
       </c>
@@ -1397,9 +1352,8 @@
       <c r="I13" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J13" s="24"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.4">
+    </row>
+    <row r="14" spans="1:9" ht="14.4">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
@@ -1409,9 +1363,8 @@
       <c r="G14" s="24"/>
       <c r="H14" s="24"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-    </row>
-    <row r="15" spans="1:10" ht="14.4">
+    </row>
+    <row r="15" spans="1:9" ht="14.4">
       <c r="A15" s="6">
         <v>10</v>
       </c>
@@ -1433,9 +1386,8 @@
       <c r="G15" s="24"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-    </row>
-    <row r="16" spans="1:10" ht="14.4">
+    </row>
+    <row r="16" spans="1:9" ht="14.4">
       <c r="A16" s="10">
         <v>11</v>
       </c>
@@ -1463,9 +1415,8 @@
       <c r="I16" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J16" s="24"/>
-    </row>
-    <row r="17" spans="1:10" ht="14.4">
+    </row>
+    <row r="17" spans="1:9" ht="14.4">
       <c r="A17" s="6">
         <v>12</v>
       </c>
@@ -1493,9 +1444,8 @@
       <c r="I17" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J17" s="24"/>
-    </row>
-    <row r="18" spans="1:10" ht="14.4">
+    </row>
+    <row r="18" spans="1:9" ht="14.4">
       <c r="A18" s="10">
         <v>13</v>
       </c>
@@ -1521,9 +1471,8 @@
         <v>122</v>
       </c>
       <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-    </row>
-    <row r="19" spans="1:10" ht="14.4">
+    </row>
+    <row r="19" spans="1:9" ht="14.4">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
@@ -1533,9 +1482,8 @@
       <c r="G19" s="24"/>
       <c r="H19" s="24"/>
       <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-    </row>
-    <row r="20" spans="1:10" ht="14.4">
+    </row>
+    <row r="20" spans="1:9" ht="14.4">
       <c r="A20" s="10">
         <v>15</v>
       </c>
@@ -1559,9 +1507,8 @@
       </c>
       <c r="H20" s="24"/>
       <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-    </row>
-    <row r="21" spans="1:10" ht="14.4">
+    </row>
+    <row r="21" spans="1:9" ht="14.4">
       <c r="A21" s="6">
         <v>16</v>
       </c>
@@ -1589,9 +1536,8 @@
       <c r="I21" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J21" s="24"/>
-    </row>
-    <row r="22" spans="1:10" ht="14.4">
+    </row>
+    <row r="22" spans="1:9" ht="14.4">
       <c r="A22" s="10">
         <v>17</v>
       </c>
@@ -1619,9 +1565,8 @@
       <c r="I22" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J22" s="24"/>
-    </row>
-    <row r="23" spans="1:10" ht="14.4">
+    </row>
+    <row r="23" spans="1:9" ht="14.4">
       <c r="A23" s="6">
         <v>18</v>
       </c>
@@ -1649,9 +1594,8 @@
       <c r="I23" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J23" s="24"/>
-    </row>
-    <row r="24" spans="1:10" ht="14.4">
+    </row>
+    <row r="24" spans="1:9" ht="14.4">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12"/>
@@ -1661,9 +1605,8 @@
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-    </row>
-    <row r="25" spans="1:10" ht="14.4">
+    </row>
+    <row r="25" spans="1:9" ht="14.4">
       <c r="A25" s="6">
         <v>20</v>
       </c>
@@ -1691,9 +1634,8 @@
       <c r="I25" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J25" s="24"/>
-    </row>
-    <row r="26" spans="1:10" ht="14.4">
+    </row>
+    <row r="26" spans="1:9" ht="14.4">
       <c r="A26" s="10">
         <v>21</v>
       </c>
@@ -1721,9 +1663,8 @@
       <c r="I26" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J26" s="24"/>
-    </row>
-    <row r="27" spans="1:10" ht="14.4">
+    </row>
+    <row r="27" spans="1:9" ht="14.4">
       <c r="A27" s="6">
         <v>22</v>
       </c>
@@ -1751,9 +1692,8 @@
       <c r="I27" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J27" s="24"/>
-    </row>
-    <row r="28" spans="1:10" ht="14.4">
+    </row>
+    <row r="28" spans="1:9" ht="14.4">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12"/>
@@ -1763,9 +1703,8 @@
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
       <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-    </row>
-    <row r="29" spans="1:10" ht="14.4">
+    </row>
+    <row r="29" spans="1:9" ht="14.4">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
@@ -1775,9 +1714,8 @@
       <c r="G29" s="24"/>
       <c r="H29" s="24"/>
       <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-    </row>
-    <row r="30" spans="1:10" ht="14.4">
+    </row>
+    <row r="30" spans="1:9" ht="14.4">
       <c r="A30" s="10">
         <v>25</v>
       </c>
@@ -1805,9 +1743,8 @@
       <c r="I30" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J30" s="24"/>
-    </row>
-    <row r="31" spans="1:10" ht="14.4">
+    </row>
+    <row r="31" spans="1:9" ht="14.4">
       <c r="A31" s="6">
         <v>26</v>
       </c>
@@ -1835,9 +1772,8 @@
       <c r="I31" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J31" s="24"/>
-    </row>
-    <row r="32" spans="1:10" ht="14.4">
+    </row>
+    <row r="32" spans="1:9" ht="14.4">
       <c r="A32" s="10">
         <v>27</v>
       </c>
@@ -1865,9 +1801,8 @@
       <c r="I32" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J32" s="24"/>
-    </row>
-    <row r="33" spans="1:10" ht="14.4">
+    </row>
+    <row r="33" spans="1:9" ht="14.4">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="8"/>
@@ -1877,9 +1812,8 @@
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
       <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-    </row>
-    <row r="34" spans="1:10" ht="14.4">
+    </row>
+    <row r="34" spans="1:9" ht="14.4">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -1907,9 +1841,8 @@
       <c r="I34" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J34" s="24"/>
-    </row>
-    <row r="35" spans="1:10" ht="14.4">
+    </row>
+    <row r="35" spans="1:9" ht="14.4">
       <c r="A35" s="6">
         <v>30</v>
       </c>
@@ -1937,9 +1870,8 @@
       <c r="I35" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J35" s="24"/>
-    </row>
-    <row r="36" spans="1:10" ht="14.4">
+    </row>
+    <row r="36" spans="1:9" ht="14.4">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -1961,9 +1893,8 @@
       <c r="G36" s="24"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-    </row>
-    <row r="37" spans="1:10" ht="14.4">
+    </row>
+    <row r="37" spans="1:9" ht="14.4">
       <c r="A37" s="6">
         <v>32</v>
       </c>
@@ -1991,9 +1922,8 @@
       <c r="I37" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J37" s="24"/>
-    </row>
-    <row r="38" spans="1:10" ht="14.4">
+    </row>
+    <row r="38" spans="1:9" ht="14.4">
       <c r="A38" s="15">
         <v>33</v>
       </c>
@@ -2019,7 +1949,6 @@
         <v>123</v>
       </c>
       <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2028,7 +1957,7 @@
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D20 D23 D25:D38">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>D6="Not Available"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Vectra Staffing LLC Employee Directory.xlsx
+++ b/Vectra Staffing LLC Employee Directory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\ERP-System-Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91447CF9-4225-4477-9C0D-FF7906C3D1B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4996793A-A5B2-49ED-99E3-9A5E16A171FE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19422" windowHeight="10302" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="137">
   <si>
     <t>Employee joining, designation, and contact records | Updated for 2025–2026</t>
   </si>
@@ -428,6 +428,9 @@
   </si>
   <si>
     <t>Updated Week 3</t>
+  </si>
+  <si>
+    <t>BRD not sent</t>
   </si>
 </sst>
 </file>
@@ -720,17 +723,6 @@
   <dxfs count="12">
     <dxf>
       <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -911,6 +903,17 @@
         <scheme val="major"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -925,18 +928,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:J38" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:J38" dataDxfId="10">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{95819C09-FC15-4B97-8E78-01BF41FCFA5C}" name="Column 4" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{95819C09-FC15-4B97-8E78-01BF41FCFA5C}" name="Column 4" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1463,7 +1466,9 @@
       <c r="I16" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J16" s="24"/>
+      <c r="J16" s="24" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="14.4">
       <c r="A17" s="6">
@@ -1493,7 +1498,9 @@
       <c r="I17" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J17" s="24"/>
+      <c r="J17" s="24" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="18" spans="1:10" ht="14.4">
       <c r="A18" s="10">
@@ -1521,7 +1528,9 @@
         <v>122</v>
       </c>
       <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
+      <c r="J18" s="24" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="19" spans="1:10" ht="14.4">
       <c r="A19" s="6"/>
@@ -1589,7 +1598,9 @@
       <c r="I21" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J21" s="24"/>
+      <c r="J21" s="24" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="14.4">
       <c r="A22" s="10">
@@ -1619,7 +1630,9 @@
       <c r="I22" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J22" s="24"/>
+      <c r="J22" s="24" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="14.4">
       <c r="A23" s="6">
@@ -1649,7 +1662,9 @@
       <c r="I23" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J23" s="24"/>
+      <c r="J23" s="24" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="24" spans="1:10" ht="14.4">
       <c r="A24" s="10"/>
@@ -1691,7 +1706,9 @@
       <c r="I25" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J25" s="24"/>
+      <c r="J25" s="24" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="26" spans="1:10" ht="14.4">
       <c r="A26" s="10">
@@ -1721,7 +1738,9 @@
       <c r="I26" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J26" s="24"/>
+      <c r="J26" s="24" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="14.4">
       <c r="A27" s="6">
@@ -1751,7 +1770,9 @@
       <c r="I27" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J27" s="24"/>
+      <c r="J27" s="24" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="14.4">
       <c r="A28" s="10"/>
@@ -2028,7 +2049,7 @@
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D20 D23 D25:D38">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>D6="Not Available"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Vectra Staffing LLC Employee Directory.xlsx
+++ b/Vectra Staffing LLC Employee Directory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\ERP-System-Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4996793A-A5B2-49ED-99E3-9A5E16A171FE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E599A45A-4BCA-4787-9029-26EA32C3930D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19422" windowHeight="10302" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="139">
   <si>
     <t>Employee joining, designation, and contact records | Updated for 2025–2026</t>
   </si>
@@ -431,6 +431,12 @@
   </si>
   <si>
     <t>BRD not sent</t>
+  </si>
+  <si>
+    <t>Column 5</t>
+  </si>
+  <si>
+    <t>Meetings Link</t>
   </si>
 </sst>
 </file>
@@ -720,7 +726,22 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -928,18 +949,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:J38" dataDxfId="10">
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{95819C09-FC15-4B97-8E78-01BF41FCFA5C}" name="Column 4" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:K38" dataDxfId="11">
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{95819C09-FC15-4B97-8E78-01BF41FCFA5C}" name="Column 4" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{D52CC8C3-3337-406F-9A68-385E49C3525E}" name="Column 5" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1094,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10.76171875" bestFit="1" customWidth="1"/>
@@ -1106,9 +1128,10 @@
     <col min="8" max="8" width="32.09375" customWidth="1"/>
     <col min="9" max="9" width="27.37890625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.47265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.4" customHeight="1">
+    <row r="1" spans="1:11" ht="21.4" customHeight="1">
       <c r="A1" s="30" t="s">
         <v>62</v>
       </c>
@@ -1118,7 +1141,7 @@
       <c r="E1" s="30"/>
       <c r="F1" s="30"/>
     </row>
-    <row r="2" spans="1:10" ht="14.65" customHeight="1">
+    <row r="2" spans="1:11" ht="14.65" customHeight="1">
       <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
@@ -1128,7 +1151,7 @@
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
     </row>
-    <row r="3" spans="1:10" ht="13.45" customHeight="1">
+    <row r="3" spans="1:11" ht="13.45" customHeight="1">
       <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
@@ -1138,7 +1161,7 @@
       <c r="E3" s="32"/>
       <c r="F3" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="16.649999999999999" customHeight="1">
+    <row r="5" spans="1:11" ht="16.649999999999999" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1169,8 +1192,11 @@
       <c r="J5" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="14.4">
+      <c r="K5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="14.4">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
@@ -1183,8 +1209,11 @@
         <v>132</v>
       </c>
       <c r="J6" s="24"/>
-    </row>
-    <row r="7" spans="1:10" ht="14.4">
+      <c r="K6" s="24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="14.4">
       <c r="A7" s="6">
         <v>2</v>
       </c>
@@ -1215,8 +1244,11 @@
       <c r="J7" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="14.4">
+      <c r="K7" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="14.4">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -1247,8 +1279,11 @@
       <c r="J8" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="14.4">
+      <c r="K8" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="14.4">
       <c r="A9" s="6">
         <v>4</v>
       </c>
@@ -1277,8 +1312,11 @@
       <c r="J9" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="14.4">
+      <c r="K9" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="14.4">
       <c r="A10" s="10">
         <v>5</v>
       </c>
@@ -1309,8 +1347,11 @@
       <c r="J10" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="14.4">
+      <c r="K10" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="14.4">
       <c r="A11" s="6">
         <v>6</v>
       </c>
@@ -1339,8 +1380,11 @@
       <c r="J11" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="14.4">
+      <c r="K11" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="14.4">
       <c r="A12" s="10">
         <v>7</v>
       </c>
@@ -1371,8 +1415,11 @@
       <c r="J12" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="14.4">
+      <c r="K12" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="14.4">
       <c r="A13" s="6">
         <v>8</v>
       </c>
@@ -1401,8 +1448,9 @@
         <v>133</v>
       </c>
       <c r="J13" s="24"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.4">
+      <c r="K13" s="24"/>
+    </row>
+    <row r="14" spans="1:11" ht="14.4">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
@@ -1413,8 +1461,9 @@
       <c r="H14" s="24"/>
       <c r="I14" s="24"/>
       <c r="J14" s="24"/>
-    </row>
-    <row r="15" spans="1:10" ht="14.4">
+      <c r="K14" s="24"/>
+    </row>
+    <row r="15" spans="1:11" ht="14.4">
       <c r="A15" s="6">
         <v>10</v>
       </c>
@@ -1437,8 +1486,9 @@
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
       <c r="J15" s="24"/>
-    </row>
-    <row r="16" spans="1:10" ht="14.4">
+      <c r="K15" s="24"/>
+    </row>
+    <row r="16" spans="1:11" ht="14.4">
       <c r="A16" s="10">
         <v>11</v>
       </c>
@@ -1469,8 +1519,11 @@
       <c r="J16" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="14.4">
+      <c r="K16" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="14.4">
       <c r="A17" s="6">
         <v>12</v>
       </c>
@@ -1501,8 +1554,11 @@
       <c r="J17" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="14.4">
+      <c r="K17" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="14.4">
       <c r="A18" s="10">
         <v>13</v>
       </c>
@@ -1531,8 +1587,11 @@
       <c r="J18" s="24" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="14.4">
+      <c r="K18" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="14.4">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
@@ -1543,8 +1602,9 @@
       <c r="H19" s="24"/>
       <c r="I19" s="24"/>
       <c r="J19" s="24"/>
-    </row>
-    <row r="20" spans="1:10" ht="14.4">
+      <c r="K19" s="24"/>
+    </row>
+    <row r="20" spans="1:11" ht="14.4">
       <c r="A20" s="10">
         <v>15</v>
       </c>
@@ -1569,8 +1629,9 @@
       <c r="H20" s="24"/>
       <c r="I20" s="24"/>
       <c r="J20" s="24"/>
-    </row>
-    <row r="21" spans="1:10" ht="14.4">
+      <c r="K20" s="24"/>
+    </row>
+    <row r="21" spans="1:11" ht="14.4">
       <c r="A21" s="6">
         <v>16</v>
       </c>
@@ -1601,8 +1662,11 @@
       <c r="J21" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="14.4">
+      <c r="K21" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="14.4">
       <c r="A22" s="10">
         <v>17</v>
       </c>
@@ -1633,8 +1697,11 @@
       <c r="J22" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="14.4">
+      <c r="K22" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="14.4">
       <c r="A23" s="6">
         <v>18</v>
       </c>
@@ -1665,8 +1732,11 @@
       <c r="J23" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="14.4">
+      <c r="K23" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="14.4">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12"/>
@@ -1677,8 +1747,9 @@
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
       <c r="J24" s="24"/>
-    </row>
-    <row r="25" spans="1:10" ht="14.4">
+      <c r="K24" s="24"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.4">
       <c r="A25" s="6">
         <v>20</v>
       </c>
@@ -1709,8 +1780,11 @@
       <c r="J25" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="14.4">
+      <c r="K25" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="14.4">
       <c r="A26" s="10">
         <v>21</v>
       </c>
@@ -1741,8 +1815,11 @@
       <c r="J26" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="14.4">
+      <c r="K26" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="14.4">
       <c r="A27" s="6">
         <v>22</v>
       </c>
@@ -1773,8 +1850,11 @@
       <c r="J27" s="24" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="14.4">
+      <c r="K27" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="14.4">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12"/>
@@ -1785,8 +1865,9 @@
       <c r="H28" s="24"/>
       <c r="I28" s="24"/>
       <c r="J28" s="24"/>
-    </row>
-    <row r="29" spans="1:10" ht="14.4">
+      <c r="K28" s="24"/>
+    </row>
+    <row r="29" spans="1:11" ht="14.4">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
@@ -1797,8 +1878,9 @@
       <c r="H29" s="24"/>
       <c r="I29" s="24"/>
       <c r="J29" s="24"/>
-    </row>
-    <row r="30" spans="1:10" ht="14.4">
+      <c r="K29" s="24"/>
+    </row>
+    <row r="30" spans="1:11" ht="14.4">
       <c r="A30" s="10">
         <v>25</v>
       </c>
@@ -1826,9 +1908,14 @@
       <c r="I30" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J30" s="24"/>
-    </row>
-    <row r="31" spans="1:10" ht="14.4">
+      <c r="J30" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="K30" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.4">
       <c r="A31" s="6">
         <v>26</v>
       </c>
@@ -1856,9 +1943,14 @@
       <c r="I31" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J31" s="24"/>
-    </row>
-    <row r="32" spans="1:10" ht="14.4">
+      <c r="J31" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="K31" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="14.4">
       <c r="A32" s="10">
         <v>27</v>
       </c>
@@ -1886,9 +1978,14 @@
       <c r="I32" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J32" s="24"/>
-    </row>
-    <row r="33" spans="1:10" ht="14.4">
+      <c r="J32" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="K32" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="14.4">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="8"/>
@@ -1899,8 +1996,9 @@
       <c r="H33" s="24"/>
       <c r="I33" s="24"/>
       <c r="J33" s="24"/>
-    </row>
-    <row r="34" spans="1:10" ht="14.4">
+      <c r="K33" s="24"/>
+    </row>
+    <row r="34" spans="1:11" ht="14.4">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -1928,9 +2026,14 @@
       <c r="I34" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J34" s="24"/>
-    </row>
-    <row r="35" spans="1:10" ht="14.4">
+      <c r="J34" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="K34" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="14.4">
       <c r="A35" s="6">
         <v>30</v>
       </c>
@@ -1958,9 +2061,14 @@
       <c r="I35" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J35" s="24"/>
-    </row>
-    <row r="36" spans="1:10" ht="14.4">
+      <c r="J35" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="K35" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="14.4">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -1983,8 +2091,9 @@
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
       <c r="J36" s="24"/>
-    </row>
-    <row r="37" spans="1:10" ht="14.4">
+      <c r="K36" s="24"/>
+    </row>
+    <row r="37" spans="1:11" ht="14.4">
       <c r="A37" s="6">
         <v>32</v>
       </c>
@@ -2012,9 +2121,14 @@
       <c r="I37" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J37" s="24"/>
-    </row>
-    <row r="38" spans="1:10" ht="14.4">
+      <c r="J37" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="K37" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="14.4">
       <c r="A38" s="15">
         <v>33</v>
       </c>
@@ -2040,7 +2154,12 @@
         <v>123</v>
       </c>
       <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
+      <c r="J38" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="K38" s="24" t="s">
+        <v>133</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2049,7 +2168,7 @@
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D20 D23 D25:D38">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>D6="Not Available"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Vectra Staffing LLC Employee Directory.xlsx
+++ b/Vectra Staffing LLC Employee Directory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\ERP-System-Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E599A45A-4BCA-4787-9029-26EA32C3930D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D738A389-4D61-4A51-A788-C6846A3B3CE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19422" windowHeight="10302" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Vectra Staffing LLC Employee Directory.xlsx
+++ b/Vectra Staffing LLC Employee Directory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\ERP-System-Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D738A389-4D61-4A51-A788-C6846A3B3CE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835385D6-3C27-474B-8608-F0AC686EAFE4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19422" windowHeight="10302" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="142">
   <si>
     <t>Employee joining, designation, and contact records | Updated for 2025–2026</t>
   </si>
@@ -430,13 +430,22 @@
     <t>Updated Week 3</t>
   </si>
   <si>
-    <t>BRD not sent</t>
-  </si>
-  <si>
     <t>Column 5</t>
   </si>
   <si>
     <t>Meetings Link</t>
+  </si>
+  <si>
+    <t>Column 6</t>
+  </si>
+  <si>
+    <t>Updated Week 3 brief with MD files</t>
+  </si>
+  <si>
+    <t>Done - Hamzah</t>
+  </si>
+  <si>
+    <t>Done - Naman</t>
   </si>
 </sst>
 </file>
@@ -726,7 +735,33 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -924,17 +959,6 @@
         <scheme val="major"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -949,19 +973,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:K38" dataDxfId="11">
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{95819C09-FC15-4B97-8E78-01BF41FCFA5C}" name="Column 4" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{D52CC8C3-3337-406F-9A68-385E49C3525E}" name="Column 5" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:L38" dataDxfId="13">
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{95819C09-FC15-4B97-8E78-01BF41FCFA5C}" name="Column 4" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{D52CC8C3-3337-406F-9A68-385E49C3525E}" name="Column 5" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{C04DFC6C-ABEC-4CAA-8993-A7C424050C9A}" name="Column 6" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1116,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10.76171875" bestFit="1" customWidth="1"/>
@@ -1129,9 +1154,10 @@
     <col min="9" max="9" width="27.37890625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.42578125" customWidth="1"/>
     <col min="11" max="11" width="10.47265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.4" customHeight="1">
+    <row r="1" spans="1:12" ht="21.4" customHeight="1">
       <c r="A1" s="30" t="s">
         <v>62</v>
       </c>
@@ -1141,7 +1167,7 @@
       <c r="E1" s="30"/>
       <c r="F1" s="30"/>
     </row>
-    <row r="2" spans="1:11" ht="14.65" customHeight="1">
+    <row r="2" spans="1:12" ht="14.65" customHeight="1">
       <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
@@ -1151,7 +1177,7 @@
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
     </row>
-    <row r="3" spans="1:11" ht="13.45" customHeight="1">
+    <row r="3" spans="1:12" ht="13.45" customHeight="1">
       <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
@@ -1161,7 +1187,7 @@
       <c r="E3" s="32"/>
       <c r="F3" s="32"/>
     </row>
-    <row r="5" spans="1:11" ht="16.649999999999999" customHeight="1">
+    <row r="5" spans="1:12" ht="16.649999999999999" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1193,10 +1219,13 @@
         <v>134</v>
       </c>
       <c r="K5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="14.4">
+        <v>136</v>
+      </c>
+      <c r="L5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.4">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
@@ -1210,10 +1239,13 @@
       </c>
       <c r="J6" s="24"/>
       <c r="K6" s="24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="14.4">
+        <v>137</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.4">
       <c r="A7" s="6">
         <v>2</v>
       </c>
@@ -1247,8 +1279,11 @@
       <c r="K7" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="14.4">
+      <c r="L7" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="14.4">
       <c r="A8" s="10">
         <v>3</v>
       </c>
@@ -1282,8 +1317,11 @@
       <c r="K8" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="14.4">
+      <c r="L8" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="14.4">
       <c r="A9" s="6">
         <v>4</v>
       </c>
@@ -1315,8 +1353,11 @@
       <c r="K9" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="14.4">
+      <c r="L9" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="14.4">
       <c r="A10" s="10">
         <v>5</v>
       </c>
@@ -1350,8 +1391,11 @@
       <c r="K10" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="14.4">
+      <c r="L10" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="14.4">
       <c r="A11" s="6">
         <v>6</v>
       </c>
@@ -1383,8 +1427,11 @@
       <c r="K11" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="14.4">
+      <c r="L11" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="14.4">
       <c r="A12" s="10">
         <v>7</v>
       </c>
@@ -1418,8 +1465,11 @@
       <c r="K12" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="14.4">
+      <c r="L12" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.4">
       <c r="A13" s="6">
         <v>8</v>
       </c>
@@ -1447,10 +1497,17 @@
       <c r="I13" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-    </row>
-    <row r="14" spans="1:11" ht="14.4">
+      <c r="J13" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="L13" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.4">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
@@ -1462,8 +1519,9 @@
       <c r="I14" s="24"/>
       <c r="J14" s="24"/>
       <c r="K14" s="24"/>
-    </row>
-    <row r="15" spans="1:11" ht="14.4">
+      <c r="L14" s="24"/>
+    </row>
+    <row r="15" spans="1:12" ht="14.4">
       <c r="A15" s="6">
         <v>10</v>
       </c>
@@ -1487,8 +1545,9 @@
       <c r="I15" s="24"/>
       <c r="J15" s="24"/>
       <c r="K15" s="24"/>
-    </row>
-    <row r="16" spans="1:11" ht="14.4">
+      <c r="L15" s="24"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.4">
       <c r="A16" s="10">
         <v>11</v>
       </c>
@@ -1522,8 +1581,11 @@
       <c r="K16" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="14.4">
+      <c r="L16" s="24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="14.4">
       <c r="A17" s="6">
         <v>12</v>
       </c>
@@ -1557,8 +1619,11 @@
       <c r="K17" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="14.4">
+      <c r="L17" s="24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="14.4">
       <c r="A18" s="10">
         <v>13</v>
       </c>
@@ -1583,15 +1648,20 @@
       <c r="H18" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="I18" s="24"/>
+      <c r="I18" s="24" t="s">
+        <v>133</v>
+      </c>
       <c r="J18" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K18" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="14.4">
+      <c r="L18" s="24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8"/>
@@ -1603,8 +1673,9 @@
       <c r="I19" s="24"/>
       <c r="J19" s="24"/>
       <c r="K19" s="24"/>
-    </row>
-    <row r="20" spans="1:11" ht="14.4">
+      <c r="L19" s="24"/>
+    </row>
+    <row r="20" spans="1:12" ht="14.4">
       <c r="A20" s="10">
         <v>15</v>
       </c>
@@ -1630,8 +1701,9 @@
       <c r="I20" s="24"/>
       <c r="J20" s="24"/>
       <c r="K20" s="24"/>
-    </row>
-    <row r="21" spans="1:11" ht="14.4">
+      <c r="L20" s="24"/>
+    </row>
+    <row r="21" spans="1:12" ht="14.4">
       <c r="A21" s="6">
         <v>16</v>
       </c>
@@ -1665,8 +1737,9 @@
       <c r="K21" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="14.4">
+      <c r="L21" s="24"/>
+    </row>
+    <row r="22" spans="1:12" ht="14.4">
       <c r="A22" s="10">
         <v>17</v>
       </c>
@@ -1700,8 +1773,9 @@
       <c r="K22" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="14.4">
+      <c r="L22" s="24"/>
+    </row>
+    <row r="23" spans="1:12" ht="14.4">
       <c r="A23" s="6">
         <v>18</v>
       </c>
@@ -1735,8 +1809,9 @@
       <c r="K23" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="14.4">
+      <c r="L23" s="24"/>
+    </row>
+    <row r="24" spans="1:12" ht="14.4">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12"/>
@@ -1748,8 +1823,9 @@
       <c r="I24" s="24"/>
       <c r="J24" s="24"/>
       <c r="K24" s="24"/>
-    </row>
-    <row r="25" spans="1:11" ht="14.4">
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="1:12" ht="14.4">
       <c r="A25" s="6">
         <v>20</v>
       </c>
@@ -1783,8 +1859,9 @@
       <c r="K25" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="14.4">
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="1:12" ht="14.4">
       <c r="A26" s="10">
         <v>21</v>
       </c>
@@ -1818,8 +1895,9 @@
       <c r="K26" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="14.4">
+      <c r="L26" s="24"/>
+    </row>
+    <row r="27" spans="1:12" ht="14.4">
       <c r="A27" s="6">
         <v>22</v>
       </c>
@@ -1853,8 +1931,9 @@
       <c r="K27" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="14.4">
+      <c r="L27" s="24"/>
+    </row>
+    <row r="28" spans="1:12" ht="14.4">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12"/>
@@ -1866,8 +1945,9 @@
       <c r="I28" s="24"/>
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
-    </row>
-    <row r="29" spans="1:11" ht="14.4">
+      <c r="L28" s="24"/>
+    </row>
+    <row r="29" spans="1:12" ht="14.4">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
@@ -1879,8 +1959,9 @@
       <c r="I29" s="24"/>
       <c r="J29" s="24"/>
       <c r="K29" s="24"/>
-    </row>
-    <row r="30" spans="1:11" ht="14.4">
+      <c r="L29" s="24"/>
+    </row>
+    <row r="30" spans="1:12" ht="14.4">
       <c r="A30" s="10">
         <v>25</v>
       </c>
@@ -1914,8 +1995,9 @@
       <c r="K30" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="14.4">
+      <c r="L30" s="24"/>
+    </row>
+    <row r="31" spans="1:12" ht="14.4">
       <c r="A31" s="6">
         <v>26</v>
       </c>
@@ -1949,8 +2031,9 @@
       <c r="K31" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="14.4">
+      <c r="L31" s="24"/>
+    </row>
+    <row r="32" spans="1:12" ht="14.4">
       <c r="A32" s="10">
         <v>27</v>
       </c>
@@ -1984,8 +2067,9 @@
       <c r="K32" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="14.4">
+      <c r="L32" s="24"/>
+    </row>
+    <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="8"/>
@@ -1997,8 +2081,9 @@
       <c r="I33" s="24"/>
       <c r="J33" s="24"/>
       <c r="K33" s="24"/>
-    </row>
-    <row r="34" spans="1:11" ht="14.4">
+      <c r="L33" s="24"/>
+    </row>
+    <row r="34" spans="1:12" ht="14.4">
       <c r="A34" s="10">
         <v>29</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="K34" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="14.4">
+      <c r="L34" s="24"/>
+    </row>
+    <row r="35" spans="1:12" ht="14.4">
       <c r="A35" s="6">
         <v>30</v>
       </c>
@@ -2067,8 +2153,9 @@
       <c r="K35" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="14.4">
+      <c r="L35" s="24"/>
+    </row>
+    <row r="36" spans="1:12" ht="14.4">
       <c r="A36" s="10">
         <v>31</v>
       </c>
@@ -2092,8 +2179,9 @@
       <c r="I36" s="24"/>
       <c r="J36" s="24"/>
       <c r="K36" s="24"/>
-    </row>
-    <row r="37" spans="1:11" ht="14.4">
+      <c r="L36" s="24"/>
+    </row>
+    <row r="37" spans="1:12" ht="14.4">
       <c r="A37" s="6">
         <v>32</v>
       </c>
@@ -2127,8 +2215,9 @@
       <c r="K37" s="24" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="14.4">
+      <c r="L37" s="24"/>
+    </row>
+    <row r="38" spans="1:12" ht="14.4">
       <c r="A38" s="15">
         <v>33</v>
       </c>
@@ -2160,6 +2249,7 @@
       <c r="K38" s="24" t="s">
         <v>133</v>
       </c>
+      <c r="L38" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2168,7 +2258,7 @@
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D20 D23 D25:D38">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>D6="Not Available"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Vectra Staffing LLC Employee Directory.xlsx
+++ b/Vectra Staffing LLC Employee Directory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\ERP-System-Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835385D6-3C27-474B-8608-F0AC686EAFE4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3B09F7-D1A9-441F-B160-D5BC05D86E29}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19422" windowHeight="10302" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="142">
   <si>
     <t>Employee joining, designation, and contact records | Updated for 2025–2026</t>
   </si>
@@ -750,17 +750,6 @@
         <scheme val="major"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -959,6 +948,17 @@
         <scheme val="major"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -973,19 +973,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:L38" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EmployeeDirectoryWithDesignation" displayName="EmployeeDirectoryWithDesignation" ref="A5:L38" dataDxfId="12">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{95819C09-FC15-4B97-8E78-01BF41FCFA5C}" name="Column 4" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{D52CC8C3-3337-406F-9A68-385E49C3525E}" name="Column 5" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr. No." dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date of Joining" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Employee Name" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Designation" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Personal Email ID" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Official Email ID" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{2E3810A5-C9F7-49A1-AEC2-94158935767D}" name="Column1" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{B81BBC40-737D-455E-BBC1-509E40D3F7D8}" name="Column2" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{31800684-A15C-4EDC-9F08-3D0F7FE50F4F}" name="Column 3" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{95819C09-FC15-4B97-8E78-01BF41FCFA5C}" name="Column 4" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{D52CC8C3-3337-406F-9A68-385E49C3525E}" name="Column 5" dataDxfId="1"/>
     <tableColumn id="12" xr3:uid="{C04DFC6C-ABEC-4CAA-8993-A7C424050C9A}" name="Column 6" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1737,7 +1737,9 @@
       <c r="K21" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L21" s="24"/>
+      <c r="L21" s="24" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="22" spans="1:12" ht="14.4">
       <c r="A22" s="10">
@@ -1773,7 +1775,9 @@
       <c r="K22" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L22" s="24"/>
+      <c r="L22" s="24" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="23" spans="1:12" ht="14.4">
       <c r="A23" s="6">
@@ -1809,7 +1813,9 @@
       <c r="K23" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L23" s="24"/>
+      <c r="L23" s="24" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="24" spans="1:12" ht="14.4">
       <c r="A24" s="10"/>
@@ -1859,7 +1865,9 @@
       <c r="K25" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L25" s="24"/>
+      <c r="L25" s="24" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="26" spans="1:12" ht="14.4">
       <c r="A26" s="10">
@@ -1895,7 +1903,9 @@
       <c r="K26" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L26" s="24"/>
+      <c r="L26" s="24" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="27" spans="1:12" ht="14.4">
       <c r="A27" s="6">
@@ -1931,7 +1941,9 @@
       <c r="K27" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L27" s="24"/>
+      <c r="L27" s="24" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="28" spans="1:12" ht="14.4">
       <c r="A28" s="10"/>
@@ -1995,7 +2007,9 @@
       <c r="K30" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L30" s="24"/>
+      <c r="L30" s="24" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="31" spans="1:12" ht="14.4">
       <c r="A31" s="6">
@@ -2031,7 +2045,9 @@
       <c r="K31" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L31" s="24"/>
+      <c r="L31" s="24" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="32" spans="1:12" ht="14.4">
       <c r="A32" s="10">
@@ -2067,7 +2083,9 @@
       <c r="K32" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L32" s="24"/>
+      <c r="L32" s="24" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="6"/>
@@ -2117,7 +2135,9 @@
       <c r="K34" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L34" s="24"/>
+      <c r="L34" s="24" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="35" spans="1:12" ht="14.4">
       <c r="A35" s="6">
@@ -2153,7 +2173,9 @@
       <c r="K35" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L35" s="24"/>
+      <c r="L35" s="24" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="36" spans="1:12" ht="14.4">
       <c r="A36" s="10">
@@ -2215,7 +2237,9 @@
       <c r="K37" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L37" s="24"/>
+      <c r="L37" s="24" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="38" spans="1:12" ht="14.4">
       <c r="A38" s="15">
@@ -2249,7 +2273,9 @@
       <c r="K38" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="L38" s="24"/>
+      <c r="L38" s="24" t="s">
+        <v>141</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2258,7 +2284,7 @@
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D20 D23 D25:D38">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>D6="Not Available"</formula>
     </cfRule>
   </conditionalFormatting>
